--- a/reports/excel/698167220.xlsx
+++ b/reports/excel/698167220.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>CRN</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>Stamp Loan</t>
+  </si>
+  <si>
+    <t>Sustained EMI</t>
   </si>
   <si>
     <t>Concerns</t>
@@ -439,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -485,19 +488,22 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>698167220</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2">
         <v>8.970000000000001</v>
@@ -509,10 +515,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2">
         <v>785</v>
@@ -521,13 +527,16 @@
         <v>111111.11</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" t="s">
         <v>20</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
       </c>
       <c r="N2" t="s">
         <v>21</v>
+      </c>
+      <c r="O2" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/reports/excel/698167220.xlsx
+++ b/reports/excel/698167220.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>CRN</t>
   </si>
@@ -55,6 +55,21 @@
     <t>Sustained EMI</t>
   </si>
   <si>
+    <t>Aff EMI</t>
+  </si>
+  <si>
+    <t>EMI Unsec</t>
+  </si>
+  <si>
+    <t>Aff EMI Topup</t>
+  </si>
+  <si>
+    <t>EMI Unsec Topup</t>
+  </si>
+  <si>
+    <t>Current EMI</t>
+  </si>
+  <si>
     <t>Concerns</t>
   </si>
   <si>
@@ -62,8 +77,8 @@
   </si>
   <si>
     <t>Here is a two-paragraph summary of the bureau portfolio:
-The customer has a total of 34 tradelines, with 28 live and 6 closed accounts. The product-wise breakdown shows a mix of loan products, including credit card (26 accounts), personal loan (1 account), home loan (1 account), auto loan (1 account), business loan (1 account), gold loan (1 account), LAP (1 account), and consumer durable (1 account). The sanctioned exposure is INR 1,83,88,130, with a total outstanding of INR 96,35,179. Unsecured sanction amount is INR 87,93,130, accounting for 22% of the total outstanding. Notable data points include credit card utilization at 9.0%, obligation and FOIR indicating over-leveraged status, and Kotak (On-Us) exposure with a max DPD of 90 days.
-The customer's behavioral features show a clean repayment profile with zero DPD across all products and windows, no missed payments. Utilization is elevated at 8.97% for credit cards, while personal loan outstanding accounts for 53.46%. Enquiry behavior is minimal, with unsecured enquiries last 12 months at 0. The loan acquisition velocity is steady, with an average interpurchase time of 3.45 months. Sanctioned exposure has decreased by 1% over the past 6 months, trending stable.</t>
+The customer's tradeline portfolio consists of 34 total tradelines (28 live and 6 closed). The product-wise breakdown reveals a diverse mix of loan products, including credit cards, personal loans, home loans, auto loans, business loans, gold loans, LAPs, and consumer durable loans. Key highlights include a high credit card utilization percentage of 9.0%, with sanctioned exposure totaling INR 1,83,88,130 and outstanding amount of INR 96,35,179. The customer's obligation and FOIR indicate an over-leveraged position, with total bureau EMI obligation standing at INR 2,10,737 and unsecured EMI obligation at INR 84,337.
+The behavioral insights reveal a mixed picture. Enquiry pressure is evident with 40 trade-to-enquiry ratio in the last 24 months, indicating frequent loan applications. However, repayment discipline is highlighted by zero missed payments and clean DPD values across all products and windows. Utilization is elevated at 53.46% for personal loans, while credit card utilization is healthy at 8.97%. The customer's loan acquisition velocity is moderate, with an average interpurchase time of 3.45 months. Overall, the portfolio presents a complex risk profile, with both positive and negative signals that require careful consideration.</t>
   </si>
   <si>
     <t>E.True_Salary</t>
@@ -72,7 +87,7 @@
     <t>120d DPD / Business Loan / 3M ago</t>
   </si>
   <si>
-    <t>68.5% / Unsec: 60.8%</t>
+    <t>189.7% / Unsec: 75.9%</t>
   </si>
   <si>
     <t>Sanctioned exposure peaked at ₹1.8Cr in Mar 2025, led by CC (₹63.5L) and LAP (₹50.0L). Current exposure stands at ₹1.7Cr (CC, PL, HL, AL, BL, GL, LAP, CD active), down 1% from peak — trend stable.</t>
@@ -442,10 +457,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -491,19 +506,34 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:20">
       <c r="A2">
         <v>698167220</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E2">
         <v>8.970000000000001</v>
@@ -515,10 +545,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J2">
         <v>785</v>
@@ -527,16 +557,31 @@
         <v>111111.11</v>
       </c>
       <c r="L2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O2" t="s">
-        <v>22</v>
+      <c r="N2">
+        <v>210736.73</v>
+      </c>
+      <c r="O2">
+        <v>84336.73</v>
+      </c>
+      <c r="P2">
+        <v>210736.73</v>
+      </c>
+      <c r="Q2">
+        <v>99536.73</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/reports/excel/698167220.xlsx
+++ b/reports/excel/698167220.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>CRN</t>
   </si>
@@ -76,27 +76,9 @@
     <t>Intelligent Report</t>
   </si>
   <si>
-    <t>Here is a two-paragraph summary of the bureau portfolio:
-The customer's tradeline portfolio consists of 34 total tradelines (28 live and 6 closed). The product-wise breakdown reveals a diverse mix of loan products, including credit cards, personal loans, home loans, auto loans, business loans, gold loans, LAPs, and consumer durable loans. Key highlights include a high credit card utilization percentage of 9.0%, with sanctioned exposure totaling INR 1,83,88,130 and outstanding amount of INR 96,35,179. The customer's obligation and FOIR indicate an over-leveraged position, with total bureau EMI obligation standing at INR 2,10,737 and unsecured EMI obligation at INR 84,337.
-The behavioral insights reveal a mixed picture. Enquiry pressure is evident with 40 trade-to-enquiry ratio in the last 24 months, indicating frequent loan applications. However, repayment discipline is highlighted by zero missed payments and clean DPD values across all products and windows. Utilization is elevated at 53.46% for personal loans, while credit card utilization is healthy at 8.97%. The customer's loan acquisition velocity is moderate, with an average interpurchase time of 3.45 months. Overall, the portfolio presents a complex risk profile, with both positive and negative signals that require careful consideration.</t>
-  </si>
-  <si>
-    <t>E.True_Salary</t>
-  </si>
-  <si>
-    <t>120d DPD / Business Loan / 3M ago</t>
-  </si>
-  <si>
-    <t>189.7% / Unsec: 75.9%</t>
-  </si>
-  <si>
-    <t>Sanctioned exposure peaked at ₹1.8Cr in Mar 2025, led by CC (₹63.5L) and LAP (₹50.0L). Current exposure stands at ₹1.7Cr (CC, PL, HL, AL, BL, GL, LAP, CD active), down 1% from peak — trend stable.</t>
-  </si>
-  <si>
-    <t>Credit Card</t>
-  </si>
-  <si>
-    <t>Active delinquency detected with Max DPD of 120 days [Business Loan: Opened: Nov 2021 | Active] | Home Loan: Forced events detected — NUL [Opened: Jun 2019 | Active] | Auto Loan: Forced events detected — NUL [Opened: Mar 2022 | Active] | Business Loan: Delinquent with Max DPD of 120 days [Opened: Nov 2021 | Active] | Business Loan: Forced events detected — NUL [Opened: Nov 2021 | Active] | Gold Loan: Forced events detected — NUL [Opened: Aug 2024 | Active] | LAP: Forced events detected — NUL [Opened: Feb 2020 | Active] | Two Wheeler Loan: Forced events detected — NUL [Opened: May 2021 | Last Closed: May 2024] | Consumer Durable: Forced events detected — NUL [Opened: Mar 2025 | Active] | Credit Card: Delinquent with Max DPD of 90 days [Opened: Aug 2018 – Nov 2025 | Last Closed: Nov 2025] | Personal Loan: Delinquent with Max DPD of 60 days [Opened: May 2024 | Active]</t>
+    <t>Here is the executive summary:
+The customer's tradeline portfolio consists of 0 live tradelines, 0 closed tradelines, and a total of 0 sanctioned exposure. The loan products present in the portfolio are primarily credit cards, with no joint loans or defaulted/delinquent loan types. Notable data points include a credit card utilization percentage of 0%, indicating no outstanding balance on any credit card account. There are no DPD values above zero, and the customer has made 0 missed payments. The enquiry count is 0, and the loan acquisition velocity is 0 new loans in the last 6 months. Kotak (On-Us) Exposure data is not available.
+The customer's credit behavior presents a low-risk profile. There are no [HIGH RISK] features identified. However, the credit card utilization percentage of 0% indicates a lack of utilization, which could be considered a [POSITIVE] feature. The absence of any DPD values above zero and 0 missed payments suggests good repayment discipline. The enquiry count of 0 and loan acquisition velocity of 0 new loans in the last 6 months indicate low enquiry pressure and no loan stacking.</t>
   </si>
   <si>
     <t>reports/bureau_analyser_698167220_report.html</t>
@@ -529,59 +511,8 @@
       <c r="B2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" t="s">
+      <c r="T2" t="s">
         <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2">
-        <v>8.970000000000001</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2">
-        <v>785</v>
-      </c>
-      <c r="K2">
-        <v>111111.11</v>
-      </c>
-      <c r="L2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>210736.73</v>
-      </c>
-      <c r="O2">
-        <v>84336.73</v>
-      </c>
-      <c r="P2">
-        <v>210736.73</v>
-      </c>
-      <c r="Q2">
-        <v>99536.73</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2" t="s">
-        <v>26</v>
-      </c>
-      <c r="T2" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
